--- a/2023-24 (1)_Formatted.xlsx
+++ b/2023-24 (1)_Formatted.xlsx
@@ -1090,16 +1090,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25.98" customWidth="1" min="2" max="2"/>
-    <col width="20.45" customWidth="1" min="3" max="3"/>
-    <col width="24.6" customWidth="1" min="4" max="4"/>
-    <col width="60.18" customWidth="1" min="5" max="5"/>
-    <col width="12.41" customWidth="1" min="6" max="6"/>
-    <col width="25.23" customWidth="1" min="7" max="7"/>
+    <col width="24.6" customWidth="1" min="3" max="3"/>
+    <col width="60.18" customWidth="1" min="4" max="4"/>
+    <col width="12.41" customWidth="1" min="5" max="5"/>
+    <col width="25.23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -1112,8 +1111,7 @@
       <c r="C1" s="5" t="n"/>
       <c r="D1" s="5" t="n"/>
       <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -1125,8 +1123,7 @@
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -1138,8 +1135,7 @@
       <c r="C3" s="11" t="n"/>
       <c r="D3" s="11" t="n"/>
       <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
     </row>
     <row r="4" ht="15.6" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
@@ -1154,25 +1150,20 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Designation</t>
+          <t>Semester/ Group</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Semester/ Group</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Attendees</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Attendees</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Feedback Percentage</t>
         </is>
@@ -1189,23 +1180,18 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
           <t>Information Theory and Coding (Theory | Elective)</t>
         </is>
       </c>
+      <c r="E5" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="F5" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="14" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1216,21 +1202,20 @@
           <t>MANDAR SONTAKKE</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n"/>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Semester IV Division B</t>
+        </is>
+      </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
           <t>Analog and Digital Communication Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E6" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F6" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G6" s="14" t="n">
         <v>99.11</v>
       </c>
     </row>
@@ -1243,21 +1228,20 @@
           <t>MANDAR SONTAKKE</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n"/>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Semester VIII Division A</t>
+        </is>
+      </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Semester VIII Division A</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
           <t>Wireless Mobile Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E7" s="14" t="n">
+        <v>66</v>
+      </c>
       <c r="F7" s="14" t="n">
-        <v>66</v>
-      </c>
-      <c r="G7" s="14" t="n">
         <v>98.67</v>
       </c>
     </row>
@@ -1270,23 +1254,18 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
           <t>Embedded Systems Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E8" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F8" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G8" s="14" t="n">
         <v>98.64</v>
       </c>
     </row>
@@ -1299,21 +1278,20 @@
           <t>SANGEETA CHOUGULE</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n"/>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division B</t>
+        </is>
+      </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
           <t>Signals and Systems (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E9" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F9" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G9" s="14" t="n">
         <v>98.2</v>
       </c>
     </row>
@@ -1328,23 +1306,18 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
           <t>Embedded System (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E10" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F10" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G10" s="14" t="n">
         <v>98.08</v>
       </c>
     </row>
@@ -1357,21 +1330,20 @@
           <t>Atul Nigavekar</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
           <t>Embedded System (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E11" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F11" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G11" s="14" t="n">
         <v>97.18000000000001</v>
       </c>
     </row>
@@ -1384,23 +1356,18 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
           <t>Design Thinking (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E12" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F12" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G12" s="14" t="n">
         <v>97.06</v>
       </c>
     </row>
@@ -1413,23 +1380,18 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
           <t>Operating System (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E13" s="14" t="n">
+        <v>55</v>
+      </c>
       <c r="F13" s="14" t="n">
-        <v>55</v>
-      </c>
-      <c r="G13" s="14" t="n">
         <v>96.86</v>
       </c>
     </row>
@@ -1444,23 +1406,18 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
           <t>Data Structures (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E14" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F14" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G14" s="14" t="n">
         <v>96.81</v>
       </c>
     </row>
@@ -1473,23 +1430,18 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E15" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F15" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G15" s="14" t="n">
         <v>96.77</v>
       </c>
     </row>
@@ -1502,23 +1454,18 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E16" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F16" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G16" s="14" t="n">
         <v>96.77</v>
       </c>
     </row>
@@ -1529,21 +1476,20 @@
           <t>NITIN SAMBRE</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n"/>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Semester VIII Division B</t>
+        </is>
+      </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>Semester VIII Division B</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
           <t>Wireless Mobile Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E17" s="14" t="n">
+        <v>69</v>
+      </c>
       <c r="F17" s="14" t="n">
-        <v>69</v>
-      </c>
-      <c r="G17" s="14" t="n">
         <v>96.5</v>
       </c>
     </row>
@@ -1554,21 +1500,20 @@
           <t>SANGEETA CHOUGULE</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n"/>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division B</t>
+        </is>
+      </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
           <t>Signal Analysis and Interpretation Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E18" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F18" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G18" s="14" t="n">
         <v>96.3</v>
       </c>
     </row>
@@ -1579,21 +1524,20 @@
           <t>MANDAR SONTAKKE</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Semester IV Division B</t>
+        </is>
+      </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
           <t>Analog and Digital Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E19" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F19" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G19" s="14" t="n">
         <v>96.16</v>
       </c>
     </row>
@@ -1606,23 +1550,18 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VIII Division B</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Semester VIII Division B</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
           <t>Satellite Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E20" s="14" t="n">
+        <v>69</v>
+      </c>
       <c r="F20" s="14" t="n">
-        <v>69</v>
-      </c>
-      <c r="G20" s="14" t="n">
         <v>95.67</v>
       </c>
     </row>
@@ -1635,23 +1574,18 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E21" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F21" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G21" s="14" t="n">
         <v>95.65000000000001</v>
       </c>
     </row>
@@ -1662,21 +1596,20 @@
           <t>Atul Nigavekar</t>
         </is>
       </c>
-      <c r="C22" s="15" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
           <t>Embedded Systems Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E22" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F22" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G22" s="14" t="n">
         <v>95.33</v>
       </c>
     </row>
@@ -1689,23 +1622,18 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
           <t>VLSI Design Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E23" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F23" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G23" s="14" t="n">
         <v>95.26000000000001</v>
       </c>
     </row>
@@ -1720,23 +1648,18 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
           <t>Linear Integrated Circuits (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E24" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F24" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G24" s="14" t="n">
         <v>94.84</v>
       </c>
     </row>
@@ -1749,23 +1672,18 @@
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
           <t>Linear Integrated Circuits Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E25" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F25" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G25" s="14" t="n">
         <v>94.81999999999999</v>
       </c>
     </row>
@@ -1778,23 +1696,18 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
           <t>Data Structures Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E26" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F26" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G26" s="14" t="n">
         <v>94.68000000000001</v>
       </c>
     </row>
@@ -1809,23 +1722,18 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
           <t xml:space="preserve"> Electromagnetic Engineering. (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E27" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F27" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G27" s="14" t="n">
         <v>94.39</v>
       </c>
     </row>
@@ -1840,23 +1748,18 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
           <t>VLSI Design (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E28" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F28" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G28" s="14" t="n">
         <v>93.27</v>
       </c>
     </row>
@@ -1869,23 +1772,18 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
           <t>VLSI Design (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E29" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F29" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G29" s="14" t="n">
         <v>92.59999999999999</v>
       </c>
     </row>
@@ -1898,23 +1796,18 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
           <t>Automotive Electronics  (ELECTIVE) (Theory | Elective)</t>
         </is>
       </c>
+      <c r="E30" s="14" t="n">
+        <v>49</v>
+      </c>
       <c r="F30" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="G30" s="14" t="n">
         <v>92.14</v>
       </c>
     </row>
@@ -1925,21 +1818,20 @@
           <t>MANDAR SONTAKKE</t>
         </is>
       </c>
-      <c r="C31" s="15" t="n"/>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
           <t>Design Thinking (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E31" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F31" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G31" s="14" t="n">
         <v>92.13</v>
       </c>
     </row>
@@ -1952,23 +1844,18 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
           <t>Design Thinking (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E32" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F32" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G32" s="14" t="n">
         <v>92.13</v>
       </c>
     </row>
@@ -1981,23 +1868,18 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
           <t>Signal Analysis and Interpretation Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E33" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F33" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G33" s="14" t="n">
         <v>91.90000000000001</v>
       </c>
     </row>
@@ -2008,21 +1890,20 @@
           <t>Vishwala Raut Desai</t>
         </is>
       </c>
-      <c r="C34" s="15" t="n"/>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
           <t>Signal Analysis and Interpretation Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E34" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F34" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G34" s="14" t="n">
         <v>91.90000000000001</v>
       </c>
     </row>
@@ -2035,23 +1916,18 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
           <t>Mini-Project-III (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E35" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F35" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G35" s="14" t="n">
         <v>91.64</v>
       </c>
     </row>
@@ -2066,23 +1942,18 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E36" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F36" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G36" s="14" t="n">
         <v>91.5</v>
       </c>
     </row>
@@ -2097,23 +1968,18 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester VIII Division A</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Semester VIII Division A</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
           <t>Satellite Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E37" s="14" t="n">
+        <v>66</v>
+      </c>
       <c r="F37" s="14" t="n">
-        <v>66</v>
-      </c>
-      <c r="G37" s="14" t="n">
         <v>91.34</v>
       </c>
     </row>
@@ -2126,23 +1992,18 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
           <t>VLSI Design Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E38" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F38" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G38" s="14" t="n">
         <v>91.23</v>
       </c>
     </row>
@@ -2155,23 +2016,18 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
           <t>Mini Project-I (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E39" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F39" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G39" s="14" t="n">
         <v>91.22</v>
       </c>
     </row>
@@ -2184,23 +2040,18 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E40" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F40" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G40" s="14" t="n">
         <v>90.56</v>
       </c>
     </row>
@@ -2213,23 +2064,18 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E41" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F41" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G41" s="14" t="n">
         <v>90.56</v>
       </c>
     </row>
@@ -2240,21 +2086,20 @@
           <t>Vishwala Raut Desai</t>
         </is>
       </c>
-      <c r="C42" s="15" t="n"/>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Semester IV Division B</t>
+        </is>
+      </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
           <t>Constitution of India (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E42" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F42" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G42" s="14" t="n">
         <v>90.54000000000001</v>
       </c>
     </row>
@@ -2267,21 +2112,20 @@
           <t>Vishwala Raut Desai</t>
         </is>
       </c>
-      <c r="C43" s="15" t="n"/>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Semester IV Division A</t>
+        </is>
+      </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
           <t>Constitution of India (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E43" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F43" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G43" s="14" t="n">
         <v>89.55</v>
       </c>
     </row>
@@ -2296,23 +2140,18 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
           <t>Signals and Systems (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E44" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F44" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G44" s="14" t="n">
         <v>89.47</v>
       </c>
     </row>
@@ -2323,21 +2162,20 @@
           <t>Vishwala Raut Desai</t>
         </is>
       </c>
-      <c r="C45" s="15" t="n"/>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
           <t>Signals and Systems (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E45" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F45" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G45" s="14" t="n">
         <v>89.47</v>
       </c>
     </row>
@@ -2352,23 +2190,18 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
           <t>Analog and Digital Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E46" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F46" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G46" s="14" t="n">
         <v>89.2</v>
       </c>
     </row>
@@ -2381,23 +2214,18 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
           <t>Analog and Digital Communication Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E47" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F47" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G47" s="14" t="n">
         <v>88.52</v>
       </c>
     </row>
@@ -2408,21 +2236,20 @@
           <t>NITIN SAMBRE</t>
         </is>
       </c>
-      <c r="C48" s="15" t="n"/>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division B</t>
+        </is>
+      </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
           <t>Mini-Project-III (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E48" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F48" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G48" s="14" t="n">
         <v>86.52</v>
       </c>
     </row>
@@ -2435,23 +2262,18 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
           <t>Mini Project-I (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E49" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F49" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G49" s="14" t="n">
         <v>86.23999999999999</v>
       </c>
     </row>
@@ -2466,23 +2288,18 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
           <t xml:space="preserve"> Electromagnetic Engineering. (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E50" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F50" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G50" s="14" t="n">
         <v>85.16</v>
       </c>
     </row>
@@ -2497,23 +2314,18 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
           <t>Linear Integrated Circuits (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E51" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F51" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G51" s="14" t="n">
         <v>73.76000000000001</v>
       </c>
     </row>
@@ -2526,31 +2338,26 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
           <t>Linear Integrated Circuits Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E52" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F52" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G52" s="14" t="n">
         <v>73.17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2563,16 +2370,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25.98" customWidth="1" min="2" max="2"/>
-    <col width="20.45" customWidth="1" min="3" max="3"/>
-    <col width="24.6" customWidth="1" min="4" max="4"/>
-    <col width="60.18" customWidth="1" min="5" max="5"/>
-    <col width="12.41" customWidth="1" min="6" max="6"/>
-    <col width="25.23" customWidth="1" min="7" max="7"/>
+    <col width="24.6" customWidth="1" min="3" max="3"/>
+    <col width="60.18" customWidth="1" min="4" max="4"/>
+    <col width="12.41" customWidth="1" min="5" max="5"/>
+    <col width="25.23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -2585,8 +2391,7 @@
       <c r="C1" s="5" t="n"/>
       <c r="D1" s="5" t="n"/>
       <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -2598,8 +2403,7 @@
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -2611,8 +2415,7 @@
       <c r="C3" s="11" t="n"/>
       <c r="D3" s="11" t="n"/>
       <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
     </row>
     <row r="4" ht="15.6" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
@@ -2627,25 +2430,20 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Designation</t>
+          <t>Semester/ Group</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Semester/ Group</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Attendees</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Attendees</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Feedback Percentage</t>
         </is>
@@ -2658,21 +2456,20 @@
           <t>MANDAR SONTAKKE</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n"/>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Semester IV Division B</t>
+        </is>
+      </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
           <t>Analog and Digital Communication Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E5" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F5" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G5" s="14" t="n">
         <v>97.89</v>
       </c>
     </row>
@@ -2683,21 +2480,20 @@
           <t>MANDAR SONTAKKE</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n"/>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Semester IV Division B</t>
+        </is>
+      </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
           <t>Analog and Digital Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E6" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F6" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G6" s="14" t="n">
         <v>97.81</v>
       </c>
     </row>
@@ -2710,23 +2506,18 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
           <t>Operating System (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E7" s="14" t="n">
+        <v>56</v>
+      </c>
       <c r="F7" s="14" t="n">
-        <v>56</v>
-      </c>
-      <c r="G7" s="14" t="n">
         <v>97.42</v>
       </c>
     </row>
@@ -2739,23 +2530,18 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
           <t>Embedded Systems Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E8" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F8" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G8" s="14" t="n">
         <v>96.95</v>
       </c>
     </row>
@@ -2768,23 +2554,18 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
           <t>Data Structures (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E9" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F9" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G9" s="14" t="n">
         <v>95.98999999999999</v>
       </c>
     </row>
@@ -2797,23 +2578,18 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
           <t>Data Structures Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E10" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F10" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G10" s="14" t="n">
         <v>95.95999999999999</v>
       </c>
     </row>
@@ -2826,23 +2602,18 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E11" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F11" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G11" s="14" t="n">
         <v>95.45999999999999</v>
       </c>
     </row>
@@ -2855,23 +2626,18 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester VIII Division A</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Semester VIII Division A</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
           <t>Satellite Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E12" s="14" t="n">
+        <v>66</v>
+      </c>
       <c r="F12" s="14" t="n">
-        <v>66</v>
-      </c>
-      <c r="G12" s="14" t="n">
         <v>95.20999999999999</v>
       </c>
     </row>
@@ -2882,21 +2648,20 @@
           <t>MANDAR SONTAKKE</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n"/>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Semester VIII Division A</t>
+        </is>
+      </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Semester VIII Division A</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
           <t>Wireless Mobile Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E13" s="14" t="n">
+        <v>66</v>
+      </c>
       <c r="F13" s="14" t="n">
-        <v>66</v>
-      </c>
-      <c r="G13" s="14" t="n">
         <v>95.20999999999999</v>
       </c>
     </row>
@@ -2909,23 +2674,18 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
           <t>Analog and Digital Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E14" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F14" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G14" s="14" t="n">
         <v>95.09</v>
       </c>
     </row>
@@ -2938,23 +2698,18 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
           <t>Embedded System (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E15" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F15" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G15" s="14" t="n">
         <v>94.88</v>
       </c>
     </row>
@@ -2967,23 +2722,18 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E16" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F16" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G16" s="14" t="n">
         <v>94.67</v>
       </c>
     </row>
@@ -2996,23 +2746,18 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E17" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F17" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G17" s="14" t="n">
         <v>94.67</v>
       </c>
     </row>
@@ -3025,23 +2770,18 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
           <t>Design Thinking (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E18" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F18" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G18" s="14" t="n">
         <v>94.3</v>
       </c>
     </row>
@@ -3052,21 +2792,20 @@
           <t>NITIN SAMBRE</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Semester VIII Division B</t>
+        </is>
+      </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Semester VIII Division B</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
           <t>Wireless Mobile Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E19" s="14" t="n">
+        <v>69</v>
+      </c>
       <c r="F19" s="14" t="n">
-        <v>69</v>
-      </c>
-      <c r="G19" s="14" t="n">
         <v>94.29000000000001</v>
       </c>
     </row>
@@ -3077,21 +2816,20 @@
           <t>SANGEETA CHOUGULE</t>
         </is>
       </c>
-      <c r="C20" s="15" t="n"/>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division B</t>
+        </is>
+      </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
           <t>Signal Analysis and Interpretation Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E20" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F20" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G20" s="14" t="n">
         <v>93.84999999999999</v>
       </c>
     </row>
@@ -3102,21 +2840,20 @@
           <t>SANGEETA CHOUGULE</t>
         </is>
       </c>
-      <c r="C21" s="15" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division B</t>
+        </is>
+      </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
           <t>Signals and Systems (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E21" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F21" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G21" s="14" t="n">
         <v>93.75</v>
       </c>
     </row>
@@ -3129,23 +2866,18 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
           <t>Analog and Digital Communication Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E22" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F22" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G22" s="14" t="n">
         <v>93.43000000000001</v>
       </c>
     </row>
@@ -3158,23 +2890,18 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
           <t>VLSI Design Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E23" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F23" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G23" s="14" t="n">
         <v>92.92</v>
       </c>
     </row>
@@ -3185,21 +2912,20 @@
           <t>NITIN SAMBRE</t>
         </is>
       </c>
-      <c r="C24" s="15" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division B</t>
+        </is>
+      </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
           <t>Mini-Project-III (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E24" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F24" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G24" s="14" t="n">
         <v>92.79000000000001</v>
       </c>
     </row>
@@ -3210,21 +2936,20 @@
           <t>Vishwala Raut Desai</t>
         </is>
       </c>
-      <c r="C25" s="15" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Semester IV Division B</t>
+        </is>
+      </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
           <t>Constitution of India (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E25" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F25" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G25" s="14" t="n">
         <v>92.61</v>
       </c>
     </row>
@@ -3235,21 +2960,20 @@
           <t>Atul Nigavekar</t>
         </is>
       </c>
-      <c r="C26" s="15" t="n"/>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
           <t>Embedded Systems Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E26" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F26" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G26" s="14" t="n">
         <v>92.58</v>
       </c>
     </row>
@@ -3262,23 +2986,18 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
           <t>Mini-Project-III (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E27" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F27" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G27" s="14" t="n">
         <v>92.38</v>
       </c>
     </row>
@@ -3289,21 +3008,20 @@
           <t>MANDAR SONTAKKE</t>
         </is>
       </c>
-      <c r="C28" s="15" t="n"/>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
           <t>Design Thinking (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E28" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F28" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G28" s="14" t="n">
         <v>91.75</v>
       </c>
     </row>
@@ -3316,23 +3034,18 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
           <t>Design Thinking (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E29" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F29" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G29" s="14" t="n">
         <v>91.75</v>
       </c>
     </row>
@@ -3345,23 +3058,18 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E30" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F30" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G30" s="14" t="n">
         <v>91.48</v>
       </c>
     </row>
@@ -3374,23 +3082,18 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E31" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F31" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G31" s="14" t="n">
         <v>91.48</v>
       </c>
     </row>
@@ -3403,23 +3106,18 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
           <t>Analog Circuits-II (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E32" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F32" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G32" s="14" t="n">
         <v>91.09</v>
       </c>
     </row>
@@ -3432,23 +3130,18 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
           <t>Information Theory and Coding (Theory | Elective)</t>
         </is>
       </c>
+      <c r="E33" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="F33" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G33" s="14" t="n">
         <v>90.92</v>
       </c>
     </row>
@@ -3459,21 +3152,20 @@
           <t>Vishwala Raut Desai</t>
         </is>
       </c>
-      <c r="C34" s="15" t="n"/>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Semester IV Division A</t>
+        </is>
+      </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
           <t>Constitution of India (Audit Course) (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E34" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F34" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G34" s="14" t="n">
         <v>89.90000000000001</v>
       </c>
     </row>
@@ -3486,23 +3178,18 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
           <t>Signal Analysis and Interpretation Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E35" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F35" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G35" s="14" t="n">
         <v>89.81999999999999</v>
       </c>
     </row>
@@ -3513,21 +3200,20 @@
           <t>Vishwala Raut Desai</t>
         </is>
       </c>
-      <c r="C36" s="15" t="n"/>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
           <t>Signal Analysis and Interpretation Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E36" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F36" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G36" s="14" t="n">
         <v>89.81999999999999</v>
       </c>
     </row>
@@ -3540,23 +3226,18 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VIII Division B</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Semester VIII Division B</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
           <t>Satellite Communication (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E37" s="14" t="n">
+        <v>69</v>
+      </c>
       <c r="F37" s="14" t="n">
-        <v>69</v>
-      </c>
-      <c r="G37" s="14" t="n">
         <v>89.64</v>
       </c>
     </row>
@@ -3569,23 +3250,18 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division B</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division B</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
           <t>VLSI Design (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E38" s="14" t="n">
+        <v>51</v>
+      </c>
       <c r="F38" s="14" t="n">
-        <v>51</v>
-      </c>
-      <c r="G38" s="14" t="n">
         <v>89.63</v>
       </c>
     </row>
@@ -3596,21 +3272,20 @@
           <t>Atul Nigavekar</t>
         </is>
       </c>
-      <c r="C39" s="15" t="n"/>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
           <t>Embedded System (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E39" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F39" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G39" s="14" t="n">
         <v>89.53</v>
       </c>
     </row>
@@ -3623,23 +3298,18 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
           <t xml:space="preserve"> Electromagnetic Engineering. (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E40" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F40" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G40" s="14" t="n">
         <v>89.20999999999999</v>
       </c>
     </row>
@@ -3652,23 +3322,18 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
           <t>Linear Integrated Circuits (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E41" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F41" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G41" s="14" t="n">
         <v>89.13</v>
       </c>
     </row>
@@ -3681,23 +3346,18 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
           <t>VLSI Design Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E42" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F42" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G42" s="14" t="n">
         <v>88.42</v>
       </c>
     </row>
@@ -3710,23 +3370,18 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
           <t>Automotive Electronics  (ELECTIVE) (Theory | Elective)</t>
         </is>
       </c>
+      <c r="E43" s="14" t="n">
+        <v>49</v>
+      </c>
       <c r="F43" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="G43" s="14" t="n">
         <v>88.40000000000001</v>
       </c>
     </row>
@@ -3739,23 +3394,18 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
           <t>Signals and Systems (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E44" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F44" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G44" s="14" t="n">
         <v>88.33</v>
       </c>
     </row>
@@ -3766,21 +3416,20 @@
           <t>Vishwala Raut Desai</t>
         </is>
       </c>
-      <c r="C45" s="15" t="n"/>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
           <t>Signals and Systems (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E45" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F45" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G45" s="14" t="n">
         <v>88.33</v>
       </c>
     </row>
@@ -3793,23 +3442,18 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester VI Division A</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
           <t>VLSI Design (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E46" s="14" t="n">
+        <v>63</v>
+      </c>
       <c r="F46" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="G46" s="14" t="n">
         <v>87.45999999999999</v>
       </c>
     </row>
@@ -3822,23 +3466,18 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
           <t>Mini Project-I (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E47" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F47" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G47" s="14" t="n">
         <v>84.69</v>
       </c>
     </row>
@@ -3851,23 +3490,18 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
           <t>Linear Integrated Circuits Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E48" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F48" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G48" s="14" t="n">
         <v>83.78</v>
       </c>
     </row>
@@ -3880,23 +3514,18 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
           <t>Mini Project-I (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E49" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F49" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G49" s="14" t="n">
         <v>82.93000000000001</v>
       </c>
     </row>
@@ -3909,23 +3538,18 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division B</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division B</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
           <t xml:space="preserve"> Electromagnetic Engineering. (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E50" s="14" t="n">
+        <v>74</v>
+      </c>
       <c r="F50" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="G50" s="14" t="n">
         <v>76.61</v>
       </c>
     </row>
@@ -3938,21 +3562,20 @@
           <t>NITIN SAMBRE</t>
         </is>
       </c>
-      <c r="C51" s="15" t="n"/>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Semester VI Division A</t>
+        </is>
+      </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>Semester VI Division A</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
           <t>Medical Electronics (Theory | Elective)</t>
         </is>
       </c>
+      <c r="E51" s="14" t="n">
+        <v>15</v>
+      </c>
       <c r="F51" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="G51" s="14" t="n">
         <v>74.86</v>
       </c>
     </row>
@@ -3965,23 +3588,18 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
           <t>Linear Integrated Circuits (Theory | Regular)</t>
         </is>
       </c>
+      <c r="E52" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F52" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G52" s="14" t="n">
         <v>60.64</v>
       </c>
     </row>
@@ -3994,31 +3612,26 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Semester IV Division A</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>Semester IV Division A</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
           <t>Linear Integrated Circuits Lab (Practical | Regular)</t>
         </is>
       </c>
+      <c r="E53" s="14" t="n">
+        <v>78</v>
+      </c>
       <c r="F53" s="14" t="n">
-        <v>78</v>
-      </c>
-      <c r="G53" s="14" t="n">
         <v>59.62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
